--- a/Master/2265r0 w Rippers/2265r0 w Rippers @ 0.250 IPR_cutlet_data.xlsx
+++ b/Master/2265r0 w Rippers/2265r0 w Rippers @ 0.250 IPR_cutlet_data.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1214,139 +1214,139 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>5.237</v>
+        <v>1.303</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>5.6884</v>
+        <v>5.6129</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>-0.8657</v>
+        <v>-3.2104</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>0.0227</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>2.138</v>
+        <v>1.302</v>
       </c>
       <c r="B40" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>5.7501</v>
+        <v>5.6608</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>-1.0695</v>
+        <v>-3.6001</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>0.0081</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>1.139</v>
+        <v>5.237</v>
       </c>
       <c r="B41" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>5.811</v>
+        <v>5.6884</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>-1.278</v>
+        <v>-0.8657</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>0.0234</v>
+        <v>0.0227</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>4.14</v>
+        <v>2.138</v>
       </c>
       <c r="B42" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>5.8701</v>
+        <v>5.7501</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>-1.2495</v>
+        <v>-1.0695</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>0.0066</v>
+        <v>0.0081</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>3.241</v>
+        <v>1.139</v>
       </c>
       <c r="B43" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>5.9091</v>
+        <v>5.811</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>-1.4491</v>
+        <v>-1.278</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>0.0132</v>
+        <v>0.0234</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>6.142</v>
+        <v>4.14</v>
       </c>
       <c r="B44" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>5.9572</v>
+        <v>5.8701</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>-1.4418</v>
+        <v>-1.2495</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>0.0047</v>
+        <v>0.0066</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>5.143</v>
+        <v>3.241</v>
       </c>
       <c r="B45" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>5.9795</v>
+        <v>5.9091</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>-1.626</v>
+        <v>-1.4491</v>
       </c>
       <c r="F45" s="7" t="n">
         <v>0.0132</v>
@@ -1354,242 +1354,282 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>2.144</v>
+        <v>6.142</v>
       </c>
       <c r="B46" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>6.0217</v>
+        <v>5.9572</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>-1.888</v>
+        <v>-1.4418</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>0.0029</v>
+        <v>0.0047</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>1.245</v>
+        <v>5.143</v>
       </c>
       <c r="B47" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.0307</v>
+        <v>5.9795</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>-2.0493</v>
+        <v>-1.626</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>0.0065</v>
+        <v>0.0132</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>4.146</v>
+        <v>2.144</v>
       </c>
       <c r="B48" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C48" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>6.0626</v>
+        <v>6.0217</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>-2.0592</v>
+        <v>-1.888</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>0.003</v>
+        <v>0.0029</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>3.147</v>
+        <v>1.245</v>
       </c>
       <c r="B49" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C49" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>6.0701</v>
+        <v>6.0307</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>-2.2164</v>
+        <v>-2.0493</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>0.0074</v>
+        <v>0.0065</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>5.301</v>
+        <v>4.146</v>
       </c>
       <c r="B50" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C50" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>6.0909</v>
+        <v>6.0626</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>-2.3411</v>
+        <v>-2.0592</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>0.0001</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>6.148</v>
+        <v>3.147</v>
       </c>
       <c r="B51" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C51" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>6.0984</v>
+        <v>6.0701</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>-2.2767</v>
+        <v>-2.2164</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>0.002</v>
+        <v>0.0074</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>4.303</v>
+        <v>5.301</v>
       </c>
       <c r="B52" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C52" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>6.0997</v>
+        <v>6.0909</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>-2.4204</v>
+        <v>-2.3411</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>0.0033</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>3.303</v>
+        <v>6.148</v>
       </c>
       <c r="B53" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C53" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>6.1116</v>
+        <v>6.0984</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>-2.5813</v>
+        <v>-2.2767</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>2.15</v>
+        <v>4.303</v>
       </c>
       <c r="B54" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C54" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>6.1153</v>
+        <v>6.0997</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>-2.6687</v>
+        <v>-2.4204</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>0.0015</v>
+        <v>0.0033</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>4.152</v>
+        <v>3.303</v>
       </c>
       <c r="B55" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C55" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>6.1235</v>
+        <v>6.1116</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>-2.754</v>
+        <v>-2.5813</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>0.0002</v>
+        <v>0.0005999999999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="B56" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>6.1153</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>-2.6687</v>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>0.0015</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="n">
+        <v>4.152</v>
+      </c>
+      <c r="B57" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>6.1235</v>
+      </c>
+      <c r="E57" s="7" t="n">
+        <v>-2.754</v>
+      </c>
+      <c r="F57" s="7" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n">
         <v>4.302</v>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B58" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C56" s="6" t="n">
+      <c r="C58" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D56" s="7" t="n">
+      <c r="D58" s="7" t="n">
         <v>6.1243</v>
       </c>
-      <c r="E56" s="7" t="n">
+      <c r="E58" s="7" t="n">
         <v>-2.678</v>
       </c>
-      <c r="F56" s="7" t="n">
+      <c r="F58" s="7" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="58">
-      <c r="E58" s="8" t="inlineStr">
+    <row r="60">
+      <c r="E60" s="8" t="inlineStr">
         <is>
           <t>Count:</t>
         </is>
       </c>
-      <c r="F58" s="9" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="E59" s="8" t="inlineStr">
+      <c r="F60" s="9" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="E61" s="8" t="inlineStr">
         <is>
           <t>Total Area:</t>
         </is>
       </c>
-      <c r="F59" s="10" t="n">
-        <v>1.5193</v>
+      <c r="F61" s="10" t="n">
+        <v>1.5198</v>
       </c>
     </row>
   </sheetData>
